--- a/attractionsForAgent.xlsx
+++ b/attractionsForAgent.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B151"/>
+  <dimension ref="A1:B300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1928,6 +1928,1496 @@
         </is>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>中央大街步行街</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>印象丽江</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>崇圣寺三塔</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>文殊院</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>香港西贡</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>广州地铁</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>上海城市历史发展陈列馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>杭州宋城</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Beijing Airport Layover Tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>鹿回头公园</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>狮子林</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>陈家祠</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>网师园</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>中国丽江古城</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>798艺术区</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>香港海事博物馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>东方明珠</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>崂山自然风景区</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>汉阳陵</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>峨眉山</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>同里古镇</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>豫园</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>大馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>云南石林地质公园</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>天一阁</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>西湖花港观鱼公园</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>金茂大厦</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>回坊风情街</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>花城广场</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>颐和园佛香阁</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>平江路</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>虎丘</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>青海湖</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>香港文化博物馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>太阳岛</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>鸣沙山</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>玉佛禅寺</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>凤凰古城</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>昆明龙门</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>金沙遗址博物馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>中华恐龙园</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>明孝陵</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>郑家大屋</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>旧城</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Happy Dragon Tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>南京城墙(明城墙)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>珠海长隆海洋王国</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>新濠天地</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>周庄水乡</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Alex's Epic Xian的一日游</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>澳门历史城区</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>留园</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>香港历史博物馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>陕西历史博物馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>苏州博物馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>八大关</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>午门</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>珠穆朗玛峰基地营</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>两江四湖景区</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>长洲岛</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>白云山</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>峨眉山金顶</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>澳门大熊猫馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>朱家角古镇</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>扎什伦布寺</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>古北水镇</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>武汉东湖</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>大雁塔</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>锦绣中华·民俗村</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>大雁塔北广场</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>青岛啤酒博物馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>西塘古镇</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>沙面岛</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>黄龙名胜风景区</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>尖沙咀海滨长廊</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>星海广场</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>故宫九龙壁</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Guangzhou Private Local Tour Guide-Lorena</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>上海人文历史地貌区</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>复兴公园</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>岳麓山</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>大澳</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>外滩城市雕塑群</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>广州图书馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>大芬油画村</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>趵突泉公园</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>南丫岛</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>南普陀寺</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>金鸡湖</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>九龙公园</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Travel Beijing Guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>三清山</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>SoHo 荷南美食区</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>后海</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>普陀山</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>COCO PARK</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>西安博物院</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>冈仁波齐峰</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>赤柱</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Beijing Impression Tours</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>厦门大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>孔庙和国子监博物馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>成都人民公园</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>束河古镇</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>China Educational Tours</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>石室圣心大教堂</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>杜甫草堂</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>圆明园</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>祖庙</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>珠江</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>上海虹桥火车站</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>元阳梯田</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>鸟巢(国家体育场)</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>北京欢乐谷</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>路环岛</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>深圳地铁</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>尖东</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>苏州古运河</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>香港科学馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>南京总统府</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>鼓浪屿</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>澳门旅游塔会展娱乐中心</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>沈阳故宫</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>中国国家博物馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>圣保罗大教堂遗址(大三巴牌坊)</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>平安寨</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Elysian Tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>澳门博物馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>西望洋主教堂</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>丽江木府</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>田子坊</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>旺角</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>西溪湿地公园</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>日月塔</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>洱海湖</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>九龙城寨公园</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>翠湖</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>洪崖洞</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>拙政园</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>黄大仙祠</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>天津之眼摩天轮</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>三亚珠江南田温泉</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>大明湖公园</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>三峡博物馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>世纪公园</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>前门大街商业街</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>芦笛岩</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>东望洋炮台</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>海港城</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/attractionsForAgent.xlsx
+++ b/attractionsForAgent.xlsx
@@ -413,4506 +413,3604 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C300"/>
+  <dimension ref="A1:B300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>页码</t>
+          <t>编号</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
           <t>景点名称</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
           <t>慕田峪长城</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
           <t>秦始皇兵马俑博物馆</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
           <t>上海外滩</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
           <t>天星小轮</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>1</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
           <t>香港天际线</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>1</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
           <t>天坛大佛</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>1</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
           <t>山頂纜車總</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>1</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
           <t>天坛公园</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>1</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
           <t>颐和园</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>1</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
           <t>故宫博物院</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>1</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
           <t>Chilli Cool China</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>1</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
           <t>Wendy’s Xi’an Tours</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>1</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
           <t>和平博物馆</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>1</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
           <t>Tibet Vista</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>1</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
           <t>Meto Tour</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>1</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
           <t>Catherine Lu Tours Xi'an</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>1</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
           <t>香港迪士尼乐园</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>1</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
           <t>Yoyo Wang的一日游</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>1</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
           <t>Jerry's Guide &amp; Driver Service</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>1</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
           <t>和平饭店</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>1</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
           <t>Mike's Beijing Tour</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>1</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
           <t>ChinaHiking</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>1</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
           <t>Mutianyu Great Wall Tour</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>1</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
           <t>Guilin PrivateTours</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>1</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
           <t>Jeff Ning China Tours</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>1</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
           <t>金山岭长城</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>1</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
           <t>Songtsan Tibet Travel</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>1</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
           <t>Wiki Beijing</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>1</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
           <t>大洋晶典·天安千树</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>1</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
           <t>Best China Experience</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>2</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
           <t>上窰民俗文物馆</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>2</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
           <t>国际眼镜城</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>2</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
           <t>西藏高原旅游的一日游</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>2</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
           <t>香港旅游发展局</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>2</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
           <t>Sandbox - 沙盒 VR</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>2</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
           <t>张家界国家森林公园</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>2</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
           <t>布达拉宫</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>2</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
           <t>L&amp;K裁缝</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>2</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
           <t>南外滩轻纺面料市场</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>2</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
           <t>黄花城长城</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>2</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
           <t>Xianggong Mountain</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>2</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
           <t>云冈石窟</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>2</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
           <t>大熊猫保护研究中心都江堰基地</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>2</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
           <t>九寨沟自然保护区</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>2</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
           <t>黑暗中对话</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>2</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
           <t>南莲园池</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>2</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
           <t>箭扣长城</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>2</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
           <t>亚特兰蒂斯水世界</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>2</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
           <t>黄山</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>2</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
           <t>龙脊梯田</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
-        <v>2</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
           <t>张家界天门山</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>2</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
           <t>龙门石窟</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v>2</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
           <t>哈尔滨冰雪大世界</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>2</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
           <t>居庸关长城</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
-        <v>2</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
           <t>司马台长城</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
-        <v>2</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
           <t>泸沽湖</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
-        <v>2</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
           <t>张家界武陵源风景名胜区</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
-        <v>2</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
           <t>龙脊</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
-        <v>2</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
           <t>外滩万国建筑博览</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
-        <v>2</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
           <t>志莲净苑</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
-        <v>3</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
           <t>悬空寺</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
-        <v>3</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
           <t>Art Alba Gallery</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
-        <v>3</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
           <t>Real China Travel</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
-        <v>3</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
           <t>莫高窟</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
-        <v>3</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
           <t>拉萨大昭寺</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
-        <v>3</v>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
           <t>成都地铁</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
-        <v>3</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
           <t>跑马地赛马场</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>3</v>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
           <t>慈山寺</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
-        <v>3</v>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
           <t>遇龙河</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
-        <v>3</v>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
           <t>上海中心大厦</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
-        <v>3</v>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
           <t>长隆国际马戏大剧院</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
-        <v>3</v>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
           <t>上海犹太难民纪念馆</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
-        <v>3</v>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
           <t>张掖丹霞地质文化公园</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
-        <v>3</v>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
           <t>雍和宫</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
-        <v>3</v>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
           <t>北京八达岭长城</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
-        <v>3</v>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
           <t>香港电车（叮叮车）</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
-        <v>3</v>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
           <t>景山公园</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="n">
-        <v>3</v>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
           <t>漓江景区</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
-        <v>3</v>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
           <t>哲蚌寺</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
-        <v>3</v>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
           <t>西湖</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
-        <v>3</v>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
           <t>飞来峰</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
-        <v>3</v>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
           <t>国家大剧院</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
-        <v>3</v>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
           <t>u-bestour</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="n">
-        <v>3</v>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
           <t>湖北省博物馆</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="n">
-        <v>3</v>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
           <t>华山</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
-        <v>3</v>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
           <t>磁悬浮列车</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
-        <v>3</v>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
           <t>太和殿</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
-        <v>3</v>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
           <t>长隆野生动物园</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="n">
-        <v>3</v>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
           <t>上海宣传画艺术中心</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="n">
-        <v>3</v>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
           <t>灵隐寺</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="n">
-        <v>4</v>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
           <t>南山寺</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="n">
-        <v>4</v>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
           <t>香港维多利亚海港</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="n">
-        <v>4</v>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
           <t>北海公园</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="n">
-        <v>4</v>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
           <t>Mary’s Xian Tours</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
-        <v>4</v>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
           <t>云台山地质公园</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
-        <v>4</v>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
           <t>猫之茶房</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="n">
-        <v>4</v>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
           <t>八角街</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="n">
-        <v>4</v>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
           <t>祈年殿</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="n">
-        <v>4</v>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
           <t>云南沙溪古镇</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="n">
-        <v>4</v>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
           <t>大屿山</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="n">
-        <v>4</v>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
           <t>深圳莲花山公园</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="n">
-        <v>4</v>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
           <t>虎跳峡</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="n">
-        <v>4</v>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
           <t>西安城墙</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="n">
-        <v>4</v>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
           <t>滨江大道</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="n">
-        <v>4</v>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
           <t>天际100香港观景台</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="n">
-        <v>4</v>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
           <t>观光缆车</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="n">
-        <v>4</v>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
           <t>上海环球金融中心</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="n">
-        <v>4</v>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
           <t>浦东新区</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="n">
-        <v>4</v>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
           <t>成都大熊猫繁育研究基地</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="n">
-        <v>4</v>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
           <t>朝阳剧场</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="n">
-        <v>4</v>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
           <t>平遥古城</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="n">
-        <v>4</v>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
           <t>香港公园</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="n">
-        <v>4</v>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
           <t>苏州古典园林</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="n">
-        <v>4</v>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
           <t>万佛寺</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="n">
-        <v>4</v>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
           <t>龙华寺</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="n">
-        <v>4</v>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
           <t>上海自然博物馆(静安新馆)</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="n">
-        <v>4</v>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
           <t>长隆欢乐世界</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="n">
-        <v>4</v>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
           <t>宝莲禅寺</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="n">
-        <v>4</v>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
           <t>狮子亭观景台</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="n">
-        <v>4</v>
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
           <t>黄浦江</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="n">
-        <v>5</v>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
           <t>宏村</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="n">
-        <v>5</v>
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
           <t>YakPanda</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="n">
-        <v>5</v>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
           <t>亚龙湾</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="n">
-        <v>5</v>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
           <t>颐和园长廊</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="n">
-        <v>5</v>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
           <t>乐山大佛</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="n">
-        <v>5</v>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
           <t>天子山</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="n">
-        <v>5</v>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
           <t>表演湖</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="n">
-        <v>5</v>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
           <t>珠江新城</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="n">
-        <v>5</v>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
           <t>青城山</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="n">
-        <v>5</v>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
           <t>乌镇</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="n">
-        <v>5</v>
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
           <t>上海城市规划展示馆</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="n">
-        <v>5</v>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
           <t>松赞林寺</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="n">
-        <v>5</v>
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
           <t>羊卓雍措湖</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="n">
-        <v>5</v>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
           <t>尖沙咀</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="n">
-        <v>5</v>
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
           <t>玉龙雪山</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="n">
-        <v>5</v>
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
           <t>西汉南越王博物馆</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="n">
-        <v>5</v>
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
           <t>灵山大佛</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="n">
-        <v>5</v>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
           <t>玄武湖</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="n">
-        <v>5</v>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
           <t>黄果树瀑布</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="n">
-        <v>5</v>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
           <t>澳门旅游塔</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="n">
-        <v>5</v>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
           <t>"鸭灵号"帆船</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="n">
-        <v>5</v>
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
           <t>色拉寺</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="n">
-        <v>5</v>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
           <t>都江堰水利工程</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="n">
-        <v>5</v>
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
           <t>瘦西湖</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="n">
-        <v>5</v>
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
           <t>广州塔</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="n">
-        <v>5</v>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
           <t>日月双塔文化公园</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="n">
-        <v>5</v>
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
           <t>中山陵</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="n">
-        <v>5</v>
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
           <t>故宫御花园</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="n">
-        <v>5</v>
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
           <t>上海博物馆</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="n">
-        <v>5</v>
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
           <t>泰山</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="n">
-        <v>6</v>
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
           <t>中央大街步行街</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="n">
-        <v>6</v>
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
           <t>印象丽江</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="n">
-        <v>6</v>
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
           <t>崇圣寺三塔</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="n">
-        <v>6</v>
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
           <t>文殊院</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="n">
-        <v>6</v>
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
           <t>香港西贡</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="n">
-        <v>6</v>
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
           <t>广州地铁</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="n">
-        <v>6</v>
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
           <t>上海城市历史发展陈列馆</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="n">
-        <v>6</v>
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
           <t>杭州宋城</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="n">
-        <v>6</v>
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
           <t>Beijing Airport Layover Tour</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="n">
-        <v>6</v>
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
           <t>鹿回头公园</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="n">
-        <v>6</v>
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
           <t>狮子林</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="n">
-        <v>6</v>
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
           <t>陈家祠</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="n">
-        <v>6</v>
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
           <t>网师园</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="n">
-        <v>6</v>
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
           <t>中国丽江古城</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="n">
-        <v>6</v>
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
           <t>798艺术区</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="n">
-        <v>6</v>
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
           <t>香港海事博物馆</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="n">
-        <v>6</v>
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
           <t>东方明珠</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="n">
-        <v>6</v>
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
           <t>崂山自然风景区</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="n">
-        <v>6</v>
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
           <t>汉阳陵</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="n">
-        <v>6</v>
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
           <t>峨眉山</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="n">
-        <v>6</v>
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
           <t>同里古镇</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="n">
-        <v>6</v>
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
           <t>豫园</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="n">
-        <v>6</v>
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
           <t>大馆</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="n">
-        <v>6</v>
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
           <t>云南石林地质公园</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="n">
-        <v>6</v>
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
           <t>天一阁</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="n">
-        <v>6</v>
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
           <t>西湖花港观鱼公园</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="n">
-        <v>6</v>
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
           <t>金茂大厦</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="n">
-        <v>6</v>
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
           <t>回坊风情街</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="n">
-        <v>6</v>
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
           <t>花城广场</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="n">
-        <v>6</v>
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
           <t>颐和园佛香阁</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="n">
-        <v>7</v>
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
           <t>平江路</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="n">
-        <v>7</v>
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
           <t>虎丘</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="n">
-        <v>7</v>
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
           <t>青海湖</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="n">
-        <v>7</v>
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
           <t>香港文化博物馆</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="n">
-        <v>7</v>
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
           <t>太阳岛</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="n">
-        <v>7</v>
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
           <t>鸣沙山</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="n">
-        <v>7</v>
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
           <t>玉佛禅寺</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="n">
-        <v>7</v>
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
           <t>凤凰古城</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="n">
-        <v>7</v>
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
           <t>昆明龙门</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="n">
-        <v>7</v>
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
           <t>金沙遗址博物馆</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="n">
-        <v>7</v>
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
           <t>中华恐龙园</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="n">
-        <v>7</v>
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
           <t>明孝陵</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="n">
-        <v>7</v>
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
           <t>郑家大屋</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="n">
-        <v>7</v>
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
           <t>旧城</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="n">
-        <v>7</v>
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
           <t>Happy Dragon Tour</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="n">
-        <v>7</v>
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
           <t>南京城墙(明城墙)</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="n">
-        <v>7</v>
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
           <t>珠海长隆海洋王国</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="n">
-        <v>7</v>
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
           <t>新濠天地</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="n">
-        <v>7</v>
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
           <t>周庄水乡</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="n">
-        <v>7</v>
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
           <t>Alex's Epic Xian的一日游</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="n">
-        <v>7</v>
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
           <t>澳门历史城区</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="n">
-        <v>7</v>
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
           <t>留园</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="n">
-        <v>7</v>
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
           <t>香港历史博物馆</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="n">
-        <v>7</v>
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
           <t>陕西历史博物馆</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="n">
-        <v>7</v>
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
           <t>苏州博物馆</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="n">
-        <v>7</v>
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
           <t>八大关</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="n">
-        <v>7</v>
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
           <t>午门</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="n">
-        <v>7</v>
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
           <t>珠穆朗玛峰基地营</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="n">
-        <v>7</v>
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
           <t>两江四湖景区</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="n">
-        <v>8</v>
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
           <t>长洲岛</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="n">
-        <v>8</v>
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
           <t>白云山</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="n">
-        <v>8</v>
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
           <t>峨眉山金顶</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="n">
-        <v>8</v>
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
           <t>澳门大熊猫馆</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="n">
-        <v>8</v>
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
           <t>朱家角古镇</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="n">
-        <v>8</v>
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
           <t>扎什伦布寺</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="n">
-        <v>8</v>
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
           <t>古北水镇</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="n">
-        <v>8</v>
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
           <t>武汉东湖</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="n">
-        <v>8</v>
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
           <t>大雁塔</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="n">
-        <v>8</v>
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
           <t>锦绣中华·民俗村</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="n">
-        <v>8</v>
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
           <t>大雁塔北广场</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="n">
-        <v>8</v>
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
           <t>青岛啤酒博物馆</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="n">
-        <v>8</v>
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
           <t>西塘古镇</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="n">
-        <v>8</v>
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
           <t>沙面岛</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="n">
-        <v>8</v>
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
           <t>黄龙名胜风景区</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="n">
-        <v>8</v>
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
           <t>尖沙咀海滨长廊</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="n">
-        <v>8</v>
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
           <t>星海广场</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="n">
-        <v>8</v>
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
           <t>故宫九龙壁</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="n">
-        <v>8</v>
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
           <t>Guangzhou Private Local Tour Guide-Lorena</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="n">
-        <v>8</v>
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
           <t>上海人文历史地貌区</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="n">
-        <v>8</v>
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
           <t>复兴公园</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="n">
-        <v>8</v>
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
           <t>岳麓山</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="n">
-        <v>8</v>
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
           <t>大澳</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="n">
-        <v>8</v>
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
           <t>外滩城市雕塑群</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="n">
-        <v>8</v>
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
           <t>广州图书馆</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="n">
-        <v>8</v>
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
           <t>大芬油画村</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="n">
-        <v>8</v>
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
           <t>趵突泉公园</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="n">
-        <v>8</v>
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
           <t>南丫岛</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="n">
-        <v>8</v>
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
           <t>南普陀寺</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="n">
-        <v>8</v>
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
           <t>金鸡湖</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="n">
-        <v>9</v>
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
           <t>九龙公园</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="n">
-        <v>9</v>
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
           <t>Travel Beijing Guide</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="n">
-        <v>9</v>
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
           <t>三清山</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="n">
-        <v>9</v>
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
           <t>SoHo 荷南美食区</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="n">
-        <v>9</v>
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
           <t>后海</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="n">
-        <v>9</v>
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
           <t>普陀山</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="n">
-        <v>9</v>
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
           <t>COCO PARK</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="n">
-        <v>9</v>
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
           <t>西安博物院</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="n">
-        <v>9</v>
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
           <t>冈仁波齐峰</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="n">
-        <v>9</v>
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
           <t>赤柱</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="n">
-        <v>9</v>
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
           <t>Beijing Impression Tours</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="n">
-        <v>9</v>
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
           <t>厦门大学</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="n">
-        <v>9</v>
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
           <t>孔庙和国子监博物馆</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="n">
-        <v>9</v>
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
           <t>成都人民公园</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="n">
-        <v>9</v>
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
           <t>束河古镇</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="n">
-        <v>9</v>
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
           <t>China Educational Tours</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="n">
-        <v>9</v>
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
           <t>石室圣心大教堂</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="n">
-        <v>9</v>
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
           <t>杜甫草堂</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="n">
-        <v>9</v>
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
           <t>圆明园</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="n">
-        <v>9</v>
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
           <t>祖庙</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="n">
-        <v>9</v>
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
           <t>珠江</t>
         </is>
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="n">
-        <v>9</v>
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
           <t>上海虹桥火车站</t>
         </is>
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="n">
-        <v>9</v>
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
           <t>元阳梯田</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="n">
-        <v>9</v>
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
           <t>鸟巢(国家体育场)</t>
         </is>
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="n">
-        <v>9</v>
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
           <t>北京欢乐谷</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="n">
-        <v>9</v>
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
           <t>路环岛</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="n">
-        <v>9</v>
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
           <t>深圳地铁</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="n">
-        <v>9</v>
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
           <t>尖东</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="n">
-        <v>9</v>
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
           <t>苏州古运河</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="n">
-        <v>9</v>
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
           <t>香港科学馆</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="n">
-        <v>10</v>
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
           <t>南京总统府</t>
         </is>
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="n">
-        <v>10</v>
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
           <t>鼓浪屿</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="n">
-        <v>10</v>
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
           <t>澳门旅游塔会展娱乐中心</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="n">
-        <v>10</v>
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
           <t>沈阳故宫</t>
         </is>
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="n">
-        <v>10</v>
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
           <t>中国国家博物馆</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="n">
-        <v>10</v>
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
           <t>圣保罗大教堂遗址(大三巴牌坊)</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="n">
-        <v>10</v>
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
           <t>平安寨</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="n">
-        <v>10</v>
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
           <t>Elysian Tour</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="n">
-        <v>10</v>
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
           <t>澳门博物馆</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="n">
-        <v>10</v>
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
           <t>西望洋主教堂</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="n">
-        <v>10</v>
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
           <t>丽江木府</t>
         </is>
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="n">
-        <v>10</v>
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
           <t>田子坊</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="n">
-        <v>10</v>
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
           <t>旺角</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="n">
-        <v>10</v>
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
           <t>西溪湿地公园</t>
         </is>
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="n">
-        <v>10</v>
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
           <t>日月塔</t>
         </is>
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="n">
-        <v>10</v>
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
           <t>洱海湖</t>
         </is>
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="n">
-        <v>10</v>
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
           <t>九龙城寨公园</t>
         </is>
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="n">
-        <v>10</v>
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
           <t>翠湖</t>
         </is>
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="n">
-        <v>10</v>
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
           <t>洪崖洞</t>
         </is>
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="n">
-        <v>10</v>
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
           <t>拙政园</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="n">
-        <v>10</v>
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
           <t>黄大仙祠</t>
         </is>
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="n">
-        <v>10</v>
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
           <t>天津之眼摩天轮</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="n">
-        <v>10</v>
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
           <t>三亚珠江南田温泉</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="n">
-        <v>10</v>
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
           <t>大明湖公园</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="n">
-        <v>10</v>
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>295</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
           <t>三峡博物馆</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="n">
-        <v>10</v>
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
           <t>世纪公园</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="n">
-        <v>10</v>
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
           <t>前门大街商业街</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="n">
-        <v>10</v>
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
           <t>芦笛岩</t>
         </is>
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="n">
-        <v>10</v>
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
           <t>东望洋炮台</t>
         </is>
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="n">
-        <v>10</v>
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
       </c>
       <c r="B300" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
         <is>
           <t>海港城</t>
         </is>
